--- a/measurements/30/Filled_2D_sections/sagittal/week30_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/30/Filled_2D_sections/sagittal/week30_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,82 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +576,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.874479476502082</v>
+        <v>2620.408163265306</v>
       </c>
       <c r="D2" t="n">
-        <v>11.83177057126673</v>
+        <v>231.0012349628267</v>
       </c>
       <c r="E2" t="n">
-        <v>11.09312983547769</v>
+        <v>216.5801539307549</v>
       </c>
       <c r="F2" t="n">
         <v>1.066585422396008</v>
@@ -525,24 +595,51 @@
         <v>0.6170924093574872</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5233422256097561</v>
+        <v>1.184895833333333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5233422256097561</v>
+        <v>10.21763392857143</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5233422256097561</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>4.118303571428571</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>10.21763392857143</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.991815476190476</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.184895833333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.521205357142857</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.625093005952381</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>7.332168352171327</v>
+      <c r="AC2" s="2" t="n">
+        <v>2794.869614512471</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +650,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.965794170136824</v>
+        <v>2655.215419501134</v>
       </c>
       <c r="D3" t="n">
-        <v>11.82585251040575</v>
+        <v>230.8856918698265</v>
       </c>
       <c r="E3" t="n">
-        <v>11.16211583846953</v>
+        <v>217.9270235129765</v>
       </c>
       <c r="F3" t="n">
         <v>1.059463338451362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6259153249603508</v>
+        <v>0.625915324960351</v>
       </c>
       <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.156994047619047</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.975818452380953</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.914000496031746</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.5109565548780488</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.5109565548780488</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.5109565548780488</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>9.975818452380953</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.156994047619047</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.497023809523809</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.701636904761904</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>12.39330462435397</v>
+      <c r="AC3" s="2" t="n">
+        <v>241.9645188564346</v>
       </c>
     </row>
     <row r="4">
@@ -600,34 +721,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.046400951814396</v>
+        <v>2685.9410430839</v>
       </c>
       <c r="D4" t="n">
-        <v>11.79972887620693</v>
+        <v>230.3756590116592</v>
       </c>
       <c r="E4" t="n">
-        <v>11.21089630882915</v>
+        <v>218.8794041247595</v>
       </c>
       <c r="F4" t="n">
-        <v>1.052523237318148</v>
+        <v>1.052523237318149</v>
       </c>
       <c r="G4" t="n">
         <v>0.6359649170233381</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.672991071428571</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9.090401785714285</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.280877976190476</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9.090401785714285</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.672991071428571</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.482142857142857</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.078497023809523</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>11.68970664056336</v>
+      <c r="AC4" s="2" t="n">
+        <v>228.2276058395703</v>
       </c>
     </row>
     <row r="5">
@@ -638,17 +792,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.111540749553837</v>
+        <v>2710.770975056689</v>
       </c>
       <c r="D5" t="n">
-        <v>11.78544143641867</v>
+        <v>230.0967137586503</v>
       </c>
       <c r="E5" t="n">
-        <v>11.24784069817241</v>
+        <v>219.6006993452708</v>
       </c>
       <c r="F5" t="n">
         <v>1.047795906136332</v>
@@ -657,14 +811,47 @@
         <v>0.6434011883061117</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7578125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9.045758928571429</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.757130456349206</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>9.045758928571429</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.7578125</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.415178571428571</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.699404761904762</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AC5" s="2" t="n">
         <v>1.059768988486053</v>
       </c>
     </row>
@@ -676,34 +863,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.201368233194527</v>
+        <v>2745.01133786848</v>
       </c>
       <c r="D6" t="n">
-        <v>11.74503034207879</v>
+        <v>229.3077352501097</v>
       </c>
       <c r="E6" t="n">
-        <v>11.37744331941372</v>
+        <v>222.1310362361726</v>
       </c>
       <c r="F6" t="n">
         <v>1.032308402893807</v>
       </c>
       <c r="G6" t="n">
-        <v>0.65601926985054</v>
+        <v>0.6560192698505399</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.374255952380953</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.101084183673469</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8.374255952380953</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.472842261904762</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.603748330001674</v>
+      <c r="AC6" s="2" t="n">
+        <v>0.6037483300016742</v>
       </c>
     </row>
     <row r="7">
@@ -714,34 +934,67 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.236168947055325</v>
+        <v>2758.27664399093</v>
       </c>
       <c r="D7" t="n">
-        <v>11.75931779931231</v>
+        <v>229.5866808437166</v>
       </c>
       <c r="E7" t="n">
-        <v>11.33703221925875</v>
+        <v>221.3420576140994</v>
       </c>
       <c r="F7" t="n">
-        <v>1.037248335533193</v>
+        <v>1.037248335533192</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6575886476516747</v>
+        <v>0.657588647651675</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.184895833333333</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.290550595238095</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.258308531746031</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8.290550595238095</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.184895833333333</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.294270833333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.251860119047619</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.35</v>
+      <c r="AC7" s="2" t="n">
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
@@ -752,34 +1005,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.271267102914932</v>
+        <v>2771.655328798186</v>
       </c>
       <c r="D8" t="n">
-        <v>11.79972889946728</v>
+        <v>230.3756594657898</v>
       </c>
       <c r="E8" t="n">
-        <v>11.43214189133993</v>
+        <v>223.1989607356843</v>
       </c>
       <c r="F8" t="n">
         <v>1.032153817860309</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6562599535778352</v>
+        <v>0.6562599535778351</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.022693452380953</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.279079861111111</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8.022693452380953</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.330357142857143</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6787075348432056</v>
+      <c r="AC8" s="2" t="n">
+        <v>1.511997767857143</v>
       </c>
     </row>
     <row r="9">
@@ -790,17 +1076,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.327483640690065</v>
+        <v>2793.083900226757</v>
       </c>
       <c r="D9" t="n">
-        <v>11.91504406638262</v>
+        <v>232.6270508198511</v>
       </c>
       <c r="E9" t="n">
-        <v>11.48092237914481</v>
+        <v>224.1513416880653</v>
       </c>
       <c r="F9" t="n">
         <v>1.037812439880823</v>
@@ -809,15 +1095,51 @@
         <v>0.6485947302819265</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.529017857142857</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.918526785714286</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.844866071428572</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7.918526785714286</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.776785714285714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.659970238095238</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.340029761904762</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.529017857142857</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.6787075348432056</v>
+      <c r="AC9" s="2" t="n">
+        <v>9.924107142857142</v>
       </c>
     </row>
     <row r="10">
@@ -828,34 +1150,70 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.367043426531827</v>
+        <v>2808.163265306122</v>
       </c>
       <c r="D10" t="n">
-        <v>11.98648141942373</v>
+        <v>234.0217800935109</v>
       </c>
       <c r="E10" t="n">
-        <v>11.61889441420392</v>
+        <v>226.8450814201718</v>
       </c>
       <c r="F10" t="n">
         <v>1.031637003669681</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6443467775427238</v>
+        <v>0.6443467775427241</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7.503720238095237</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.57514880952381</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7.503720238095237</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.636160714285714</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.661830357142857</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.077752976190476</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.6787075348432056</v>
+      <c r="AC10" s="2" t="n">
+        <v>4.792896781108277</v>
       </c>
     </row>
     <row r="11">
@@ -866,17 +1224,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.397977394408091</v>
+        <v>2819.954648526077</v>
       </c>
       <c r="D11" t="n">
-        <v>12.01852309994581</v>
+        <v>234.6473557608468</v>
       </c>
       <c r="E11" t="n">
-        <v>11.69971662032895</v>
+        <v>228.4230387778509</v>
       </c>
       <c r="F11" t="n">
         <v>1.027249077047124</v>
@@ -885,7 +1243,51 @@
         <v>0.6436068517564159</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.021949404761905</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.609747023809524</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.310267857142857</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7.609747023809524</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6.530877976190475</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.989211309523809</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.399553571428571</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.021949404761905</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
@@ -896,26 +1298,70 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.494646044021416</v>
+        <v>2856.802721088435</v>
       </c>
       <c r="D12" t="n">
-        <v>12.2397686562887</v>
+        <v>238.9669118608747</v>
       </c>
       <c r="E12" t="n">
-        <v>11.87463299821063</v>
+        <v>231.8380728222075</v>
       </c>
       <c r="F12" t="n">
         <v>1.030749216260671</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6286581820501175</v>
+        <v>0.6286581820501174</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.04985119047619</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.682291666666666</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.5078125</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7.682291666666666</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.51860119047619</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.171502976190476</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.116815476190476</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.04985119047619</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v>16.62946428571428</v>
       </c>
     </row>
     <row r="13">
@@ -926,26 +1372,70 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.528256989886972</v>
+        <v>2869.614512471655</v>
       </c>
       <c r="D13" t="n">
-        <v>12.35161712402251</v>
+        <v>241.1506200404394</v>
       </c>
       <c r="E13" t="n">
-        <v>11.92933154978403</v>
+        <v>232.9059969243549</v>
       </c>
       <c r="F13" t="n">
         <v>1.035398930147609</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6200927564864964</v>
+        <v>0.6200927564864963</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.750372023809524</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7.879464285714286</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.548735119047619</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7.879464285714286</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.682291666666666</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.335193452380952</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.096354166666667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.750372023809524</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="14">
@@ -956,26 +1446,70 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.571980963712076</v>
+        <v>2886.281179138322</v>
       </c>
       <c r="D14" t="n">
-        <v>12.40631567559591</v>
+        <v>242.2185441425868</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0387286703761</v>
+        <v>235.0418454692477</v>
       </c>
       <c r="F14" t="n">
         <v>1.030533706281157</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6182067212997221</v>
+        <v>0.6182067212997224</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.594122023809524</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7.940848214285714</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.678571428571428</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7.940848214285714</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7.890625</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.913690476190476</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.053571428571428</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.594122023809524</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>8.494750330687829</v>
       </c>
     </row>
     <row r="15">
@@ -986,26 +1520,70 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.661808447352767</v>
+        <v>2920.521541950113</v>
       </c>
       <c r="D15" t="n">
-        <v>12.59306821009008</v>
+        <v>245.8646650541396</v>
       </c>
       <c r="E15" t="n">
-        <v>12.0589341942857</v>
+        <v>235.4363342693874</v>
       </c>
       <c r="F15" t="n">
         <v>1.044293633848462</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6071248967105081</v>
+        <v>0.607124896710508</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.251860119047619</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.77938988095238</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8.033854166666666</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.90141369047619</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.614583333333333</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.251860119047619</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="n">
+        <v>6.821225649350649</v>
       </c>
     </row>
     <row r="16">
@@ -1016,26 +1594,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.685008923259964</v>
+        <v>2929.365079365079</v>
       </c>
       <c r="D16" t="n">
-        <v>12.87738170565629</v>
+        <v>251.4155475866227</v>
       </c>
       <c r="E16" t="n">
-        <v>12.14220767777141</v>
+        <v>237.0621498993465</v>
       </c>
       <c r="F16" t="n">
         <v>1.060546981849994</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5823701438009055</v>
+        <v>0.5823701438009057</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.357886904761905</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.271949404761905</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.848679315476191</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8.271949404761905</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.669642857142857</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.357886904761905</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>4.783761160714286</v>
       </c>
     </row>
     <row r="17">
@@ -1046,17 +1665,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.611540749553837</v>
+        <v>2901.360544217687</v>
       </c>
       <c r="D17" t="n">
-        <v>13.65888488292694</v>
+        <v>266.6734667619069</v>
       </c>
       <c r="E17" t="n">
-        <v>12.09342720741179</v>
+        <v>236.1097692875635</v>
       </c>
       <c r="F17" t="n">
         <v>1.129446983776089</v>
@@ -1065,16 +1684,48 @@
         <v>0.5126865819107641</v>
       </c>
       <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.376488095238095</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12.07961309523809</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.705264136904762</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>12.07961309523809</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9.053199404761905</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.311755952380953</v>
+      </c>
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.6187118902439025</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6187118902439025</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.6187118902439025</v>
+      <c r="S17" t="n">
+        <v>1.376488095238095</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>3.15</v>
       </c>
     </row>
     <row r="18">
@@ -1085,35 +1736,67 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.453004164187984</v>
+        <v>2840.929705215419</v>
       </c>
       <c r="D18" t="n">
-        <v>13.03555927044008</v>
+        <v>254.5037762324015</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99831754405324</v>
+        <v>234.2528663362775</v>
       </c>
       <c r="F18" t="n">
         <v>1.086448931075418</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5511653291607934</v>
+        <v>0.5511653291607933</v>
       </c>
       <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10.59523809523809</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.504557291666666</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10.59523809523809</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.824032738095238</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.252232142857142</v>
+      </c>
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.5426829268292683</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.5426829268292683</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.5426829268292683</v>
+      <c r="S18" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v>2.517206101190476</v>
       </c>
     </row>
     <row r="19">
@@ -1124,17 +1807,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.383700178465199</v>
+        <v>2814.512471655329</v>
       </c>
       <c r="D19" t="n">
-        <v>13.65888487420431</v>
+        <v>266.673466591608</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01852312320616</v>
+        <v>234.6473562149774</v>
       </c>
       <c r="F19" t="n">
         <v>1.13648613346101</v>
@@ -1143,16 +1826,45 @@
         <v>0.4973400439862354</v>
       </c>
       <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16.12723214285714</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.261904761904762</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.8260289634146342</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.8260289634146342</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8260289634146342</v>
+      <c r="M19" t="n">
+        <v>16.12723214285714</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.311755952380953</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v>1.894298735119047</v>
       </c>
     </row>
     <row r="20">
@@ -1163,17 +1875,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.309339678762641</v>
+        <v>2786.167800453515</v>
       </c>
       <c r="D20" t="n">
-        <v>13.38640751780533</v>
+        <v>261.3536705857231</v>
       </c>
       <c r="E20" t="n">
-        <v>11.96974262667865</v>
+        <v>233.6949750922975</v>
       </c>
       <c r="F20" t="n">
         <v>1.118353830596922</v>
@@ -1182,16 +1894,45 @@
         <v>0.512577956051447</v>
       </c>
       <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.549479166666667</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.81175595238095</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.390873015873016</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.8610899390243902</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.8610899390243902</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.8610899390243902</v>
+      <c r="M20" t="n">
+        <v>16.81175595238095</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.811383928571428</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.549479166666667</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>1.7890625</v>
       </c>
     </row>
     <row r="21">
@@ -1202,35 +1943,64 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.144556811421773</v>
+        <v>2723.356009070294</v>
       </c>
       <c r="D21" t="n">
-        <v>13.19128554914056</v>
+        <v>257.5441464356014</v>
       </c>
       <c r="E21" t="n">
-        <v>12.01015369485064</v>
+        <v>234.4839530899411</v>
       </c>
       <c r="F21" t="n">
         <v>1.098344441236945</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5159539182680876</v>
+        <v>0.5159539182680877</v>
       </c>
       <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16.94940476190476</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.193080357142857</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.868140243902439</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.868140243902439</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.868140243902439</v>
+      <c r="M21" t="n">
+        <v>16.94940476190476</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.283110119047619</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v>1.46484375</v>
       </c>
     </row>
     <row r="22">
@@ -1240,7 +2010,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>3.373790922619047</v>
       </c>
     </row>
     <row r="23">
@@ -1254,6 +2032,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v>2.498353019593254</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1263,6 +2049,46 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/30/Filled_2D_sections/sagittal/week30_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/30/Filled_2D_sections/sagittal/week30_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2094,4 +2300,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week30_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2794.869614512471</v>
+      </c>
+      <c r="D10" t="n">
+        <v>87.28196953872201</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2620.408163265306</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2929.365079365079</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>241.9645188564346</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13.14055661639605</v>
+      </c>
+      <c r="E11" t="n">
+        <v>229.3077352501097</v>
+      </c>
+      <c r="F11" t="n">
+        <v>266.6734667619069</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.059768988486053</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.03516934203247599</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.027249077047124</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.13648613346101</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6037483300016739</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05471518690462648</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4973400439862354</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.657588647651675</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0090.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0091.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0092.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0093.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0095.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0096.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0097.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0099.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0100.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0101.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0103.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0104.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0105.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0107.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0108.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0109.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0111.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0113.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0115.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.145931016569864</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3663475485325233</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.9333020044867295</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.565247584249853</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>16.62946428571428</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.440357403344135</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.12723214285714</v>
+      </c>
+      <c r="F48" t="n">
+        <v>16.94940476190476</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>33</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7.487091901154401</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.963073936845961</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.991815476190476</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12.07961309523809</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>63</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.360018660241875</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7800236353371358</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.156994047619047</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.913690476190476</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>